--- a/data/results/benchmark.xlsx
+++ b/data/results/benchmark.xlsx
@@ -480,7 +480,7 @@
         <v>0.469727</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0168</v>
+        <v>0.0224</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         <v>0.469727</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1113</v>
+        <v>0.1192</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         <v>4.6875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0061</v>
+        <v>0.0131</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         <v>4.734375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0041</v>
+        <v>0.0065</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         <v>0.469727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8536</v>
+        <v>0.7027</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>0.472656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2247</v>
+        <v>0.2817</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>0.469727</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8685</v>
+        <v>0.7256</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v>0.942383</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0296</v>
+        <v>0.0327</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>0.942383</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1194</v>
+        <v>0.1283</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>4.871094</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005</v>
+        <v>0.0052</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>4.863281</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0039</v>
+        <v>0.0047</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>0.958008</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6009</v>
+        <v>1.3413</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>0.963867</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7419</v>
+        <v>0.6691</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>0.942383</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6552</v>
+        <v>1.5857</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>1.422852</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0395</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1.422852</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2406</v>
+        <v>0.1388</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>5.007812</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>5.011719</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008</v>
+        <v>0.0049</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>2.391602</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1594</v>
+        <v>1.0782</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>1.436523</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8642</v>
+        <v>0.7713</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>1.422852</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1898</v>
+        <v>2.3047</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>1.911133</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0434</v>
+        <v>0.0536</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>1.911133</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1292</v>
+        <v>0.1633</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>4.851562</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0077</v>
+        <v>0.0048</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>4.992188</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0078</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1.938477</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7731</v>
+        <v>1.7161</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>1.975586</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0129</v>
+        <v>1.0419</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1.911133</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5465</v>
+        <v>5.1986</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>0.02679</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0605</v>
+        <v>0.2921</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>0.02679</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6259</v>
+        <v>1.4848</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>0.527377</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0177</v>
+        <v>0.022</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>0.527377</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0295</v>
+        <v>0.0344</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>0.027029</v>
       </c>
       <c r="F34" t="n">
-        <v>1.361</v>
+        <v>3.1821</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>0.027127</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9416</v>
+        <v>2.0781</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>0.02679</v>
       </c>
       <c r="F36" t="n">
-        <v>1.7978</v>
+        <v>2.5708</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>0.053819</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.2502</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>0.053899</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7044</v>
+        <v>1.0513</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0.875242</v>
       </c>
       <c r="F39" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0162</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>1.07105</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0112</v>
+        <v>0.0182</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>0.053899</v>
       </c>
       <c r="F41" t="n">
-        <v>1.6002</v>
+        <v>2.7499</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>0.054019</v>
       </c>
       <c r="F42" t="n">
-        <v>1.4202</v>
+        <v>1.9823</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>0.053819</v>
       </c>
       <c r="F43" t="n">
-        <v>2.8475</v>
+        <v>4.4157</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>0.080928</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1018</v>
+        <v>0.2358</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>0.081027</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6767</v>
+        <v>0.7759</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>1.055199</v>
       </c>
       <c r="F46" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>1.076201</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0111</v>
+        <v>0.0094</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>0.833143</v>
       </c>
       <c r="F48" t="n">
-        <v>2.9904</v>
+        <v>3.7845</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>0.834553</v>
       </c>
       <c r="F49" t="n">
-        <v>1.879</v>
+        <v>1.4305</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>0.08094700000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>3.9927</v>
+        <v>3.0532</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>0.108056</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2069</v>
+        <v>0.1221</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>0.10818</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7415</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>1.089651</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0072</v>
+        <v>0.0091</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>1.082651</v>
       </c>
       <c r="F54" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0089</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>0.108056</v>
       </c>
       <c r="F55" t="n">
-        <v>3.6988</v>
+        <v>3.2998</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>0.88572</v>
       </c>
       <c r="F56" t="n">
-        <v>2.7966</v>
+        <v>1.5497</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>0.108056</v>
       </c>
       <c r="F57" t="n">
-        <v>3.8865</v>
+        <v>3.0202</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>0.499296</v>
       </c>
       <c r="F58" t="n">
-        <v>4.317</v>
+        <v>2.3524</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>0.499296</v>
       </c>
       <c r="F59" t="n">
-        <v>6.2692</v>
+        <v>2.4145</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>9.988281000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>0.164</v>
+        <v>0.0746</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>10.064453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1375</v>
+        <v>0.0868</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>0.499296</v>
       </c>
       <c r="F62" t="n">
-        <v>7.5422</v>
+        <v>3.6729</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>0.499616</v>
       </c>
       <c r="F63" t="n">
-        <v>4.1483</v>
+        <v>2.5356</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>0.499296</v>
       </c>
       <c r="F64" t="n">
-        <v>5.6706</v>
+        <v>3.8633</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>0.998684</v>
       </c>
       <c r="F65" t="n">
-        <v>5.5044</v>
+        <v>3.7949</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>0.998684</v>
       </c>
       <c r="F66" t="n">
-        <v>7.8903</v>
+        <v>2.9021</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>10.019196</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2869</v>
+        <v>0.1231</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>10.059732</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3211</v>
+        <v>0.107</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>1.499331</v>
       </c>
       <c r="F69" t="n">
-        <v>11.4141</v>
+        <v>6.036</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>1.00018</v>
       </c>
       <c r="F70" t="n">
-        <v>4.8139</v>
+        <v>2.5336</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>0.998684</v>
       </c>
       <c r="F71" t="n">
-        <v>7.0729</v>
+        <v>4.5767</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>1.498185</v>
       </c>
       <c r="F72" t="n">
-        <v>5.0663</v>
+        <v>4.0675</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>1.498185</v>
       </c>
       <c r="F73" t="n">
-        <v>5.0106</v>
+        <v>3.0636</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>10.022339</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2541</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>10.055605</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2452</v>
+        <v>0.1081</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>3.998016</v>
       </c>
       <c r="F76" t="n">
-        <v>10.999</v>
+        <v>8.188499999999999</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>6.999811</v>
       </c>
       <c r="F77" t="n">
-        <v>4.4538</v>
+        <v>3.5016</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>1.498507</v>
       </c>
       <c r="F78" t="n">
-        <v>6.5053</v>
+        <v>4.907</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>1.997801</v>
       </c>
       <c r="F79" t="n">
-        <v>5.1462</v>
+        <v>4.607</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>1.997801</v>
       </c>
       <c r="F80" t="n">
-        <v>4.2065</v>
+        <v>6.8455</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>10.009598</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1296</v>
+        <v>0.2411</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>10.011873</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1057</v>
+        <v>0.2509</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>4.997678</v>
       </c>
       <c r="F83" t="n">
-        <v>10.2392</v>
+        <v>12.3664</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>5.497547</v>
       </c>
       <c r="F84" t="n">
-        <v>4.7448</v>
+        <v>6.1723</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>1.997874</v>
       </c>
       <c r="F85" t="n">
-        <v>6.6537</v>
+        <v>5.681</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>

--- a/data/results/benchmark.xlsx
+++ b/data/results/benchmark.xlsx
@@ -480,7 +480,7 @@
         <v>0.469727</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0224</v>
+        <v>0.0137</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
         <v>0.469727</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1192</v>
+        <v>0.0698</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         <v>4.6875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0131</v>
+        <v>0.0095</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         <v>4.734375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0065</v>
+        <v>0.0031</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         <v>0.469727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7027</v>
+        <v>0.4156</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>0.472656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2817</v>
+        <v>0.1505</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>0.469727</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7256</v>
+        <v>0.4288</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v>0.942383</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0327</v>
+        <v>0.019</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>0.942383</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1283</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>4.871094</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0052</v>
+        <v>0.0027</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>4.863281</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0047</v>
+        <v>0.0024</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>0.958008</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3413</v>
+        <v>0.768</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>0.963867</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6691</v>
+        <v>0.3857</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>0.942383</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5857</v>
+        <v>0.8761</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>1.422852</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0395</v>
+        <v>0.0232</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1.422852</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1388</v>
+        <v>0.0857</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>5.007812</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0049</v>
+        <v>0.0027</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>5.011719</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0049</v>
+        <v>0.0025</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>2.391602</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0782</v>
+        <v>0.6324</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>1.436523</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7713</v>
+        <v>0.429</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>1.422852</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3047</v>
+        <v>1.0737</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>1.911133</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0536</v>
+        <v>0.0283</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>1.911133</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1633</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>4.851562</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0048</v>
+        <v>0.003</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>4.992188</v>
       </c>
       <c r="F26" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0034</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>1.938477</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7161</v>
+        <v>0.8928</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>1.975586</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0419</v>
+        <v>0.5343</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1.911133</v>
       </c>
       <c r="F29" t="n">
-        <v>5.1986</v>
+        <v>1.2049</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>0.02679</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2921</v>
+        <v>0.0467</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>0.02679</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4848</v>
+        <v>0.3162</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>0.527377</v>
       </c>
       <c r="F32" t="n">
-        <v>0.022</v>
+        <v>0.0064</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>0.527377</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0344</v>
+        <v>0.007</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>0.027029</v>
       </c>
       <c r="F34" t="n">
-        <v>3.1821</v>
+        <v>0.7665</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>0.027127</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0781</v>
+        <v>0.485</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>0.02679</v>
       </c>
       <c r="F36" t="n">
-        <v>2.5708</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>0.053819</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2502</v>
+        <v>0.0564</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>0.053899</v>
       </c>
       <c r="F38" t="n">
-        <v>1.0513</v>
+        <v>0.3378</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0.875242</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0162</v>
+        <v>0.0057</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>1.07105</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0182</v>
+        <v>0.0055</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>0.053899</v>
       </c>
       <c r="F41" t="n">
-        <v>2.7499</v>
+        <v>1.0628</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>0.054019</v>
       </c>
       <c r="F42" t="n">
-        <v>1.9823</v>
+        <v>0.794</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>0.053819</v>
       </c>
       <c r="F43" t="n">
-        <v>4.4157</v>
+        <v>1.5114</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>0.080928</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2358</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>0.081027</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7759</v>
+        <v>0.3585</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>1.055199</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0108</v>
+        <v>0.0062</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>1.076201</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0094</v>
+        <v>0.0043</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>0.833143</v>
       </c>
       <c r="F48" t="n">
-        <v>3.7845</v>
+        <v>1.5238</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>0.834553</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4305</v>
+        <v>1.0182</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>0.08094700000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>3.0532</v>
+        <v>2.0047</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>0.108056</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1221</v>
+        <v>0.0866</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>0.10818</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.3882</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>1.089651</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0091</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>1.082651</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0089</v>
+        <v>0.0077</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>0.108056</v>
       </c>
       <c r="F55" t="n">
-        <v>3.2998</v>
+        <v>1.9533</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>0.88572</v>
       </c>
       <c r="F56" t="n">
-        <v>1.5497</v>
+        <v>1.0479</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>0.108056</v>
       </c>
       <c r="F57" t="n">
-        <v>3.0202</v>
+        <v>1.9848</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>0.499296</v>
       </c>
       <c r="F58" t="n">
-        <v>2.3524</v>
+        <v>1.6351</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>0.499296</v>
       </c>
       <c r="F59" t="n">
-        <v>2.4145</v>
+        <v>1.6205</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>9.988281000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0746</v>
+        <v>0.0569</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>10.064453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0868</v>
+        <v>0.0635</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>0.499296</v>
       </c>
       <c r="F62" t="n">
-        <v>3.6729</v>
+        <v>1.7501</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>0.499616</v>
       </c>
       <c r="F63" t="n">
-        <v>2.5356</v>
+        <v>0.96</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>0.499296</v>
       </c>
       <c r="F64" t="n">
-        <v>3.8633</v>
+        <v>1.8661</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>0.998684</v>
       </c>
       <c r="F65" t="n">
-        <v>3.7949</v>
+        <v>1.7189</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>0.998684</v>
       </c>
       <c r="F66" t="n">
-        <v>2.9021</v>
+        <v>1.665</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>10.019196</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1231</v>
+        <v>0.0641</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>10.059732</v>
       </c>
       <c r="F68" t="n">
-        <v>0.107</v>
+        <v>0.0593</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>1.499331</v>
       </c>
       <c r="F69" t="n">
-        <v>6.036</v>
+        <v>3.3113</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>1.00018</v>
       </c>
       <c r="F70" t="n">
-        <v>2.5336</v>
+        <v>1.4597</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>0.998684</v>
       </c>
       <c r="F71" t="n">
-        <v>4.5767</v>
+        <v>2.5192</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>1.498185</v>
       </c>
       <c r="F72" t="n">
-        <v>4.0675</v>
+        <v>1.8345</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>1.498185</v>
       </c>
       <c r="F73" t="n">
-        <v>3.0636</v>
+        <v>1.7919</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>10.022339</v>
       </c>
       <c r="F74" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0554</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>10.055605</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1081</v>
+        <v>0.0594</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>3.998016</v>
       </c>
       <c r="F76" t="n">
-        <v>8.188499999999999</v>
+        <v>4.3469</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>6.999811</v>
       </c>
       <c r="F77" t="n">
-        <v>3.5016</v>
+        <v>1.7743</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>1.498507</v>
       </c>
       <c r="F78" t="n">
-        <v>4.907</v>
+        <v>3.2596</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>1.997801</v>
       </c>
       <c r="F79" t="n">
-        <v>4.607</v>
+        <v>2.0182</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>1.997801</v>
       </c>
       <c r="F80" t="n">
-        <v>6.8455</v>
+        <v>1.7452</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>10.009598</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2411</v>
+        <v>0.0585</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>10.011873</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2509</v>
+        <v>0.0611</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>4.997678</v>
       </c>
       <c r="F83" t="n">
-        <v>12.3664</v>
+        <v>4.3094</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>5.497547</v>
       </c>
       <c r="F84" t="n">
-        <v>6.1723</v>
+        <v>1.9097</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>1.997874</v>
       </c>
       <c r="F85" t="n">
-        <v>5.681</v>
+        <v>3.0629</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>

--- a/data/results/benchmark.xlsx
+++ b/data/results/benchmark.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,25 +467,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.469727</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0137</v>
+        <v>0.0054</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHIJ
-B2: ∅ | D</t>
+          <t>B1: b | A
+B2: a | B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -498,25 +498,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.469727</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0698</v>
+        <v>0.0028</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHIJ
-B2: ∅ | D</t>
+          <t>B1: b | A
+B2: a | B</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -529,25 +529,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6875</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0095</v>
+        <v>0.0056</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B1: acehj | ACEHJ
-B2: bdfgi | BDFGI</t>
+          <t>B1: a | A
+B2: b | B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -560,25 +560,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4.734375</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0031</v>
+        <v>0.0023</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B1: abdfhi | ABDFHI
-B2: cegj | CEGJ</t>
+          <t>B1: a | A
+B2: b | B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -591,25 +591,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.469727</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4156</v>
+        <v>0.1687</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHIJ
-B2: ∅ | D</t>
+          <t>B1: b | A
+B2: a | B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -622,25 +622,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.472656</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1505</v>
+        <v>0.0194</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCDEFGHJ
-B2: ∅ | I</t>
+          <t>B1: b | A
+B2: a | B</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -653,25 +653,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.469727</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4288</v>
+        <v>0.0047</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHIJ
-B2: ∅ | D</t>
+          <t>B1: b | A
+B2: a | B</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -679,31 +679,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.942383</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.019</v>
+        <v>1.1379</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHJ
-B2: ∅ | D
-B3: ∅ | I</t>
+          <t>B1: b | A
+B2: a | B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -711,31 +710,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.942383</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0031</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHJ
-B2: ∅ | D
-B3: ∅ | I</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: a | B</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -743,31 +742,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>4.871094</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
         <v>0.0027</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B1: achj | ACHJ
-B2: bdgi | BDGI
-B3: ef | EF</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: a | B</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -775,95 +774,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>4.863281</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>B1: abfhi | ABFHI
-B2: cegj | CEGJ
-B3: d | D</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=3, n=2.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.958008</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>B1: abcdefghij | ACEFGHIJ
-B2: ∅ | B
-B3: ∅ | D</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=3, n=2.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0.963867</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3857</v>
+        <v>0.2056</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHI
-B2: ∅ | D
-B3: ∅ | J</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: a | B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -871,31 +858,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.942383</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8761</v>
+        <v>0.0412</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B1: abcdefghij | ABCEFGHJ
-B2: ∅ | D
-B3: ∅ | I</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: a | B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -903,32 +890,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.422852</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0232</v>
+        <v>0.0124</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghij | BCEFGHJ
-B3: ∅ | D
-B4: ∅ | I</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: a | B</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -936,32 +922,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>1.422852</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0857</v>
+        <v>0.4051</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghij | BCEFGHJ
-B3: ∅ | D
-B4: ∅ | I</t>
+          <t>B1: a | ∅
+B2: b | A
+B3: ∅ | B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -969,32 +954,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>5.007812</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0027</v>
+        <v>0.0054</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B1: ahj | AHJ
-B2: bfi | BFI
-B3: ce | CE
-B4: dg | DG</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1002,131 +987,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
-      <c r="E19" t="n">
-        <v>5.011719</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>B1: ahj | AHJ
-B2: bfi | BFI
-B3: ceg | CEG
-B4: d | D</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RuntimeError: could not refine into 4 non-vacuous blocks (stuck at 3).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="n">
-        <v>2.391602</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.6324</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>B1: f | AH
-B2: abcdeghij | BCEFGJ
-B3: ∅ | D
-B4: ∅ | I</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=4, n=2.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="E21" t="n">
-        <v>1.436523</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>B1: abcdefghij | ABCEFGH
-B2: ∅ | D
-B3: ∅ | I
-B4: ∅ | J</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=4, n=2.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>1.422852</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0737</v>
+        <v>0.3733</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghij | BCEFGHJ
-B3: ∅ | D
-B4: ∅ | I</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1134,33 +1098,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>1.911133</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0283</v>
+        <v>0.0794</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: ∅ | B
-B3: abcdefghij | CEFGHJ
-B4: ∅ | D
-B5: ∅ | I</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1168,33 +1131,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>1.911133</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: ∅ | B
-B3: abcdefghij | CEFGHJ
-B4: ∅ | D
-B5: ∅ | I</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1202,33 +1164,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>4.851562</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003</v>
+        <v>0.0442</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B1: aef | AEF
-B2: bd | BD
-B3: cg | CG
-B4: hi | HI
-B5: j | J</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1236,290 +1197,238 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="n">
-        <v>4.992188</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>B1: ahj | AHJ
-B2: bf | BF
-B3: ceg | CEG
-B4: d | D
-B5: i | I</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ValueError: k=5 exceeds the 4 available atoms (2 future + 2 present).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="n">
-        <v>1.938477</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.8928</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>B1: ∅ | A
-B2: abcdefghij | BCFGHJ
-B3: ∅ | D
-B4: ∅ | E
-B5: ∅ | I</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ValueError: k=5 exceeds the 4 available atoms (2 future + 2 present).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="n">
-        <v>1.975586</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5343</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>B1: ∅ | A
-B2: abcdefghij | BCDGHJ
-B3: ∅ | E
-B4: ∅ | F
-B5: ∅ | I</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=2.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="n">
-        <v>1.911133</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.2049</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>B1: ∅ | A
-B2: ∅ | B
-B3: abcdefghij | CEFGHJ
-B4: ∅ | D
-B5: ∅ | I</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=2.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.02679</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0467</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>B1: abcdefghijklmno | ABCDEFGIJKLMNO
-B2: ∅ | H</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ValueError: k=5 exceeds the 4 available atoms.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.02679</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.3162</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>B1: abcdefghijklmno | ABCDEFGIJKLMNO
-B2: ∅ | H</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ValueError: k=5 exceeds the 4 available atoms.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.527377</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>B1: abcdefghijklno | ABCDEFGHIJKLNO
-B2: m | M</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ValueError: k=5 exceeds the 4 available atoms.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.527377</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>B1: abcdefghijklno | ABCDEFGHIJKLNO
-B2: m | M</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>RuntimeError: ExactK failed to generate any valid k-partition candidate.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>0.027029</v>
+        <v>0.25</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7665</v>
+        <v>0.0034</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEFGHIJKLMNO</t>
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1527,30 +1436,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0.027127</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="n">
-        <v>0.485</v>
+        <v>0.0052</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmno | ABCDEGHIJKLMNO
-B2: ∅ | F</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1558,30 +1467,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0.02679</v>
+        <v>1.25</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.0029</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmno | ABCDEFGIJKLMNO
-B2: ∅ | H</t>
+          <t>B1: ac | AC
+B2: b | B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1589,31 +1498,30 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>0.053819</v>
+        <v>1.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0564</v>
+        <v>0.0028</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEFGIJKLMNO
-B3: ∅ | H</t>
+          <t>B1: a | A
+B2: bc | BC</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1621,31 +1529,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.053899</v>
+        <v>0.25</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3378</v>
+        <v>0.2015</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmno | ABCDEFGIKLMNO
-B2: ∅ | H
-B3: ∅ | J</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1653,31 +1560,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0.875242</v>
+        <v>0.25</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0057</v>
+        <v>0.0354</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>B1: abcefghijklno | ABCEFGHIJKLNO
-B2: d | D
-B3: m | M</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1685,31 +1591,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>1.07105</v>
+        <v>0.25</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0055</v>
+        <v>0.0155</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>B1: abdfj | ABDFJ
-B2: cgmno | CGMNO
-B3: ehikl | EHIKL</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1717,31 +1622,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.053899</v>
+        <v>0.25</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0628</v>
+        <v>0.0227</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmno | ABCDEFGIKLMNO
-B2: ∅ | H
-B3: ∅ | J</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -1749,31 +1653,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0.054019</v>
+        <v>0.75</v>
       </c>
       <c r="F42" t="n">
-        <v>0.794</v>
+        <v>0.0034</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmno | ABCDEFGIJKLNO
-B2: ∅ | H
-B3: ∅ | M</t>
+          <t>B1: ∅ | A
+B2: abc | B
+B3: ∅ | C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -1781,31 +1685,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.053819</v>
+        <v>0.75</v>
       </c>
       <c r="F43" t="n">
-        <v>1.5114</v>
+        <v>0.0056</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEFGIJKLMNO
-B3: ∅ | H</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | BC</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -1813,32 +1717,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0.080928</v>
+        <v>1.5</v>
       </c>
       <c r="F44" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEFGIKLMNO
-B3: ∅ | H
-B4: ∅ | J</t>
+          <t>B1: a | A
+B2: b | B
+B3: c | C</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -1846,32 +1749,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.081027</v>
+        <v>1.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3585</v>
+        <v>0.0036</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmno | ABCDEGIKLMNO
-B2: ∅ | F
-B3: ∅ | H
-B4: ∅ | J</t>
+          <t>B1: a | A
+B2: b | B
+B3: c | C</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -1879,32 +1781,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.055199</v>
+        <v>0.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0062</v>
+        <v>0.2306</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>B1: abdghjl | ABDGHJL
-B2: cf | CF
-B3: eikno | EIKNO
-B4: m | M</t>
+          <t>B1: b | A
+B2: ac | B
+B3: ∅ | C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -1912,32 +1813,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>1.076201</v>
+        <v>0.5</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0043</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B1: abdj | ABDJ
-B2: cmo | CMO
-B3: efhi | EFHI
-B4: gkln | GKLN</t>
+          <t>B1: b | ∅
+B2: ac | AB
+B3: ∅ | C</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -1945,32 +1845,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.833143</v>
+        <v>0.5</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5238</v>
+        <v>0.1479</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>B1: abcdefhijlno | ABCFHJLMN
-B2: m | DEK
-B3: k | G
-B4: g | IO</t>
+          <t>B1: b | A
+B2: ac | B
+B3: ∅ | C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -1978,32 +1877,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.834553</v>
+        <v>0.5</v>
       </c>
       <c r="F49" t="n">
-        <v>1.0182</v>
+        <v>0.0438</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>B1: abdfghjlmno | ABCFHJLMN
-B2: ∅ | D
-B3: k | EGI
-B4: cei | KO</t>
+          <t>B1: b | ∅
+B2: ac | AB
+B3: ∅ | C</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2011,32 +1909,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
         <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>0.08094700000000001</v>
+        <v>0.75</v>
       </c>
       <c r="F50" t="n">
-        <v>2.0047</v>
+        <v>0.0036</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEGIJKLMNO
-B3: ∅ | F
-B4: ∅ | H</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2044,33 +1942,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.108056</v>
+        <v>1.25</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0866</v>
+        <v>0.0045</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEGIKLMNO
-B3: ∅ | F
-B4: ∅ | H
-B5: ∅ | J</t>
+          <t>B1: b | ∅
+B2: c | ∅
+B3: ∅ | A
+B4: a | BC</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2078,101 +1975,84 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.10818</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.3882</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>B1: abcdefghijklmno | ABDEGIKLMNO
-B2: ∅ | C
-B3: ∅ | F
-B4: ∅ | H
-B5: ∅ | J</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=4, n=3.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1.089651</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>B1: acikno | ACIKNO
-B2: bel | BEL
-B3: d | D
-B4: fghj | FGHJ
-B5: m | M</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=4, n=3.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>1.082651</v>
+        <v>0.75</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0077</v>
+        <v>0.2844</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>B1: abd | ABD
-B2: cmo | CMO
-B3: efj | EFJ
-B4: gln | GLN
-B5: hik | HIK</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2180,33 +2060,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>0.108056</v>
+        <v>0.75</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9533</v>
+        <v>0.1285</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEGIKLMNO
-B3: ∅ | F
-B4: ∅ | H
-B5: ∅ | J</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2214,33 +2093,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>0.88572</v>
+        <v>0.75</v>
       </c>
       <c r="F56" t="n">
-        <v>1.0479</v>
+        <v>0.2605</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>B1: cdefhijkmno | ABCFHJMN
-B2: bgl | DEIK
-B3: ∅ | G
-B4: ∅ | L
-B5: a | O</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2248,33 +2126,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>0.108056</v>
+        <v>0.75</v>
       </c>
       <c r="F57" t="n">
-        <v>1.9848</v>
+        <v>0.5389</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>B1: ∅ | A
-B2: abcdefghijklmno | BCDEGIKLMNO
-B3: ∅ | F
-B4: ∅ | H
-B5: ∅ | J</t>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -2287,25 +2164,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>0.499296</v>
+        <v>1.5</v>
       </c>
       <c r="F58" t="n">
-        <v>1.6351</v>
+        <v>0.0047</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOPQRS
-B2: ∅ | T</t>
+          <t>B1: ac | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: ∅ | C</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -2318,25 +2198,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>0.499296</v>
+        <v>1.5</v>
       </c>
       <c r="F59" t="n">
-        <v>1.6205</v>
+        <v>0.0048</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOPQRS
-B2: ∅ | T</t>
+          <t>B1: b | ∅
+B2: c | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: a | C</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2349,28 +2232,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" t="n">
-        <v>9.988281000000001</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>B1: adghjlnpqrst | ADGHJLNPQRST
-B2: bcefikmo | BCEFIKMO</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=3.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2380,28 +2258,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" t="n">
-        <v>10.064453</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.0635</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>B1: acdehjlmnqt | ACDEHJLMNQT
-B2: bfgikoprs | BFGIKOPRS</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=3.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2411,25 +2284,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>0.499296</v>
+        <v>1.25</v>
       </c>
       <c r="F62" t="n">
-        <v>1.7501</v>
+        <v>0.4359</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOPQRS
-B2: ∅ | T</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: c | A
+B4: ∅ | B
+B5: ∅ | C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -2442,25 +2318,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>0.499616</v>
+        <v>1.25</v>
       </c>
       <c r="F63" t="n">
-        <v>0.96</v>
+        <v>0.1652</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOPRST
-B2: ∅ | Q</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: c | B
+B5: ∅ | C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -2473,25 +2352,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>0.499296</v>
+        <v>1.25</v>
       </c>
       <c r="F64" t="n">
-        <v>1.8661</v>
+        <v>0.27</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOPQRS
-B2: ∅ | T</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: c | B
+B5: ∅ | C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2499,31 +2381,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>0.998684</v>
+        <v>1.25</v>
       </c>
       <c r="F65" t="n">
-        <v>1.7189</v>
+        <v>10.7931</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOQRS
-B2: ∅ | P
-B3: ∅ | T</t>
+          <t>B1: a | ∅
+B2: c | ∅
+B3: b | A
+B4: ∅ | B
+B5: ∅ | C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -2531,31 +2415,30 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.998684</v>
+        <v>0.46875</v>
       </c>
       <c r="F66" t="n">
-        <v>1.665</v>
+        <v>0.0034</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOQRS
-B2: ∅ | P
-B3: ∅ | T</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -2563,31 +2446,30 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>10.019196</v>
+        <v>0.46875</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0641</v>
+        <v>0.0041</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>B1: adhjqst | ADHJQST
-B2: bceko | BCEKO
-B3: fgilmnpr | FGILMNPR</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -2595,31 +2477,30 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>10.059732</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0593</v>
+        <v>0.0022</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>B1: acdhjlmnqt | ACDHJLMNQT
-B2: bfgikoprs | BFGIKOPRS
-B3: e | E</t>
+          <t>B1: ab | AB
+B2: c | C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2627,31 +2508,30 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.499331</v>
+        <v>1.25</v>
       </c>
       <c r="F69" t="n">
-        <v>3.3113</v>
+        <v>0.0021</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ADEFGHIJKLMNOQRST
-B2: ∅ | BP
-B3: ∅ | C</t>
+          <t>B1: a | A
+B2: bc | BC</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -2659,31 +2539,30 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>1.00018</v>
+        <v>0.46875</v>
       </c>
       <c r="F70" t="n">
-        <v>1.4597</v>
+        <v>0.1812</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCEFGHIJKLMNOPQST
-B2: ∅ | D
-B3: ∅ | R</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -2691,31 +2570,30 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.998684</v>
+        <v>0.46875</v>
       </c>
       <c r="F71" t="n">
-        <v>2.5192</v>
+        <v>0.0346</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMNOQRS
-B2: ∅ | P
-B3: ∅ | T</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -2723,32 +2601,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.498185</v>
+        <v>0.46875</v>
       </c>
       <c r="F72" t="n">
-        <v>1.8345</v>
+        <v>0.0452</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMOQRS
-B2: ∅ | N
-B3: ∅ | P
-B4: ∅ | T</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -2756,32 +2632,30 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>1.498185</v>
+        <v>0.46875</v>
       </c>
       <c r="F73" t="n">
-        <v>1.7919</v>
+        <v>0.0122</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMOQRS
-B2: ∅ | N
-B3: ∅ | P
-B4: ∅ | T</t>
+          <t>B1: ∅ | A
+B2: abc | BC</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -2789,32 +2663,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>10.022339</v>
+        <v>0.96875</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0554</v>
+        <v>0.003</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>B1: adejq | ADEJQ
-B2: bcfko | BCFKO
-B3: gilmnpr | GILMNPR
-B4: hst | HST</t>
+          <t>B1: ∅ | A
+B2: abc | B
+B3: ∅ | C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -2822,32 +2695,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>10.055605</v>
+        <v>0.96875</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0594</v>
+        <v>0.0039</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>B1: apt | APT
-B2: bfgikors | BFGIKORS
-B3: cdhjlmnq | CDHJLMNQ
-B4: e | E</t>
+          <t>B1: ∅ | A
+B2: abc | B
+B3: ∅ | C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -2855,32 +2727,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.998016</v>
+        <v>1.5</v>
       </c>
       <c r="F76" t="n">
-        <v>4.3469</v>
+        <v>0.0019</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklnopqrst | ABCEFGHKLMNOPQS
-B2: m | DRT
-B3: ∅ | I
-B4: ∅ | J</t>
+          <t>B1: a | A
+B2: b | B
+B3: c | C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -2888,32 +2759,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Clustering_kmeans</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>6.999811</v>
+        <v>1.5</v>
       </c>
       <c r="F77" t="n">
-        <v>1.7743</v>
+        <v>0.0019</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>B1: r | ABS
-B2: abcdefghijklmnopqt | CDEFGILMNOT
-B3: s | HP
-B4: ∅ | JKQR</t>
+          <t>B1: a | A
+B2: b | B
+B3: c | C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -2921,32 +2791,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>Genetic</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>1.498507</v>
+        <v>0.9375</v>
       </c>
       <c r="F78" t="n">
-        <v>3.2596</v>
+        <v>0.2094</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGIJKLMOQRST
-B2: ∅ | H
-B3: ∅ | N
-B4: ∅ | P</t>
+          <t>B1: a | ∅
+B2: b | A
+B3: c | BC</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -2954,33 +2823,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.997801</v>
+        <v>0.9375</v>
       </c>
       <c r="F79" t="n">
-        <v>2.0182</v>
+        <v>0.0844</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMORS
-B2: ∅ | N
-B3: ∅ | P
-B4: ∅ | Q
-B5: ∅ | T</t>
+          <t>B1: a | ∅
+B2: b | A
+B3: c | BC</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -2988,33 +2855,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KQNodes</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>1.997801</v>
+        <v>0.9375</v>
       </c>
       <c r="F80" t="n">
-        <v>1.7452</v>
+        <v>0.1359</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDEFGHIJKLMORS
-B2: ∅ | N
-B3: ∅ | P
-B4: ∅ | Q
-B5: ∅ | T</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: c | ABC</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3022,33 +2887,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Clustering_spectral</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>10.009598</v>
+        <v>0.9375</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0585</v>
+        <v>0.0444</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>B1: ahqs | AHQS
-B2: bfkpt | BFKPT
-B3: ceo | CEO
-B4: djmnr | DJMNR
-B5: gil | GIL</t>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: c | ABC</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -3056,33 +2919,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Clustering_kmeans</t>
+          <t>KGeoMIP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>10.011873</v>
+        <v>1.46875</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0611</v>
+        <v>0.0037</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>B1: apt | APT
-B2: bfikos | BFIKOS
-B3: chjlnq | CHJLNQ
-B4: dgmr | DGMR
-B5: e | E</t>
+          <t>B1: ab | ∅
+B2: ∅ | A
+B3: c | B
+B4: ∅ | C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3090,33 +2952,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Genetic</t>
+          <t>KQNodes</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>4.997678</v>
+        <v>1.46875</v>
       </c>
       <c r="F83" t="n">
-        <v>4.3094</v>
+        <v>0.0046</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>B1: abcdefghijklnopqrst | ABCEFGHKLMNQRS
-B2: m | DPT
-B3: ∅ | I
-B4: ∅ | J
-B5: ∅ | O</t>
+          <t>B1: ab | ∅
+B2: ∅ | A
+B3: c | B
+B4: ∅ | C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3124,70 +2985,1466 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Clustering_spectral</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
-      </c>
-      <c r="E84" t="n">
-        <v>5.497547</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1.9097</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>B1: abcdefghijklnopqrst | ABCDEGJLNOPS
-B2: ∅ | F
-B3: m | HQRT
-B4: ∅ | IK
-B5: ∅ | M</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=4, n=3.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Clustering_kmeans</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=4, n=3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: c | BC</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Annealing</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: c | BC</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>Tabu</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>N20A</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>20</v>
-      </c>
-      <c r="D85" t="n">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: c | BC</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ExhaustiveK</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: c | BC</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>KGeoMIP</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" t="n">
         <v>5</v>
       </c>
-      <c r="E85" t="n">
-        <v>1.997874</v>
-      </c>
-      <c r="F85" t="n">
-        <v>3.0629</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>B1: abcdefghijklmnopqrst | ABCDFGHIJKLMOQRS
-B2: ∅ | E
-B3: ∅ | N
-B4: ∅ | P
-B5: ∅ | T</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>1.71875</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>B1: ab | ∅
+B2: c | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: ∅ | C</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>KQNodes</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.71875</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>B1: ab | ∅
+B2: c | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: ∅ | C</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Clustering_spectral</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Clustering_kmeans</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.21875</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: c | C</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Annealing</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.21875</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: c | C</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.21875</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: c | C</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ExhaustiveK</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.21875</v>
+      </c>
+      <c r="F97" t="n">
+        <v>11.0295</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>B1: a | ∅
+B2: b | ∅
+B3: ∅ | A
+B4: ∅ | B
+B5: c | C</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>KGeoMIP</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>B1: abc | ABC
+B2: d | D</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>KQNodes</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>B1: abc | ABC
+B2: d | D</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Clustering_spectral</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>B1: ad | AD
+B2: bc | BC</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Clustering_kmeans</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>B1: acd | ACD
+B2: b | B</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.2046</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>B1: d | AD
+B2: abc | BC</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Annealing</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>B1: d | AD
+B2: abc | BC</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.07920000000000001</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>B1: d | AD
+B2: abc | BC</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ExhaustiveK</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>B1: abc | ABC
+B2: d | D</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KGeoMIP</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>4</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>B1: ∅ | A
+B2: abc | BC
+B3: d | D</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>KQNodes</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>B1: ∅ | A
+B2: abc | BC
+B3: d | D</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Clustering_spectral</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>B1: ac | AC
+B2: b | B
+B3: d | D</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Clustering_kmeans</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>B1: a | A
+B2: b | B
+B3: cd | CD</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>B1: ∅ | A
+B2: abc | BC
+B3: d | D</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Annealing</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>4</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>B1: ∅ | A
+B2: abc | BC
+B3: d | D</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>B1: ∅ | A
+B2: abc | BC
+B3: d | D</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ExhaustiveK</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>B1: ∅ | A
+B2: abc | BC
+B3: d | D</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KGeoMIP</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>B1: ∅ | A
+B2: abc | B
+B3: ∅ | C
+B4: d | D</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KQNodes</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>B1: d | ∅
+B2: ∅ | A
+B3: abc | BC
+B4: ∅ | D</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Clustering_spectral</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>B1: a | A
+B2: b | B
+B3: c | C
+B4: d | D</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Clustering_kmeans</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>B1: a | A
+B2: b | B
+B3: c | C
+B4: d | D</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>4</v>
+      </c>
+      <c r="D118" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>B1: b | ∅
+B2: ac | AB
+B3: ∅ | C
+B4: d | D</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Annealing</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" t="n">
+        <v>4</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>B1: b | A
+B2: ac | B
+B3: ∅ | C
+B4: d | D</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>B1: b | ∅
+B2: d | AD
+B3: ac | B
+B4: ∅ | C</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ExhaustiveK</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>4</v>
+      </c>
+      <c r="D121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F121" t="n">
+        <v>10.5973</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>B1: b | ∅
+B2: ac | AB
+B3: ∅ | C
+B4: d | D</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KGeoMIP</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>4</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>B1: ab | ∅
+B2: ∅ | A
+B3: c | B
+B4: ∅ | C
+B5: d | D</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KQNodes</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>B1: d | ∅
+B2: ∅ | A
+B3: abc | B
+B4: ∅ | C
+B5: ∅ | D</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Clustering_spectral</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Clustering_kmeans</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>4</v>
+      </c>
+      <c r="D125" t="n">
+        <v>5</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>ValueError: node-aligned clustering needs k &lt;= n; got k=5, n=4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>4</v>
+      </c>
+      <c r="D126" t="n">
+        <v>5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C
+B5: d | D</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Annealing</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>4</v>
+      </c>
+      <c r="D127" t="n">
+        <v>5</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C
+B5: d | D</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" t="n">
+        <v>5</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C
+B5: d | D</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ExhaustiveK</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F129" t="n">
+        <v>505.8262</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>B1: b | ∅
+B2: ∅ | A
+B3: ac | B
+B4: ∅ | C
+B5: d | D</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3200,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3240,504 +4497,706 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.472656</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.963867</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1.436523</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.975586</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.027127</v>
+        <v>0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>0.054019</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.834553</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>0.88572</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.499616</v>
+        <v>0.46875</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00018</v>
+        <v>0.9375</v>
       </c>
       <c r="F4" t="n">
-        <v>6.999811</v>
+        <v>0.96875</v>
       </c>
       <c r="G4" t="n">
-        <v>5.497547</v>
+        <v>1.21875</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Clustering_kmeans</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>N10A</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4.734375</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4.863281</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.011719</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.992188</v>
-      </c>
-    </row>
-    <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.527377</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.07105</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.076201</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.082651</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>10.064453</v>
+        <v>1.25</v>
       </c>
       <c r="E7" t="n">
-        <v>10.059732</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10.055605</v>
-      </c>
-      <c r="G7" t="n">
-        <v>10.011873</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Clustering_spectral</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4.6875</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="n">
-        <v>4.871094</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.007812</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4.851562</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N4A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.527377</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
-        <v>0.875242</v>
+        <v>1.375</v>
       </c>
       <c r="F9" t="n">
-        <v>1.055199</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.089651</v>
-      </c>
+        <v>1.375</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Clustering_spectral</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>9.988281000000001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10.019196</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10.022339</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10.009598</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Genetic</t>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.469727</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
-        <v>0.958008</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.391602</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.938477</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.027029</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.053899</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.833143</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.108056</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N4A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.499296</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1.499331</v>
+        <v>1.25</v>
       </c>
       <c r="F13" t="n">
-        <v>3.998016</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4.997678</v>
-      </c>
+        <v>1.375</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KGeoMIP</t>
+          <t>ExhaustiveK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.469727</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.942383</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1.422852</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.911133</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02679</v>
+        <v>0.25</v>
       </c>
       <c r="E15" t="n">
-        <v>0.053819</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.080928</v>
+        <v>0.75</v>
       </c>
       <c r="G15" t="n">
-        <v>0.108056</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.499296</v>
+        <v>0.46875</v>
       </c>
       <c r="E16" t="n">
-        <v>0.998684</v>
+        <v>0.9375</v>
       </c>
       <c r="F16" t="n">
-        <v>1.498185</v>
+        <v>0.96875</v>
       </c>
       <c r="G16" t="n">
-        <v>1.997801</v>
+        <v>1.21875</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KQNodes</t>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N4A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.469727</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.942383</v>
+        <v>0.125</v>
       </c>
       <c r="F17" t="n">
-        <v>1.422852</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.911133</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Genetic</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02679</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.053899</v>
+        <v>0.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.081027</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.10818</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N3A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.499296</v>
+        <v>0.25</v>
       </c>
       <c r="E19" t="n">
-        <v>0.998684</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1.498185</v>
+        <v>0.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.997801</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tabu</t>
-        </is>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N10A</t>
+          <t>N3B</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.469727</v>
+        <v>0.46875</v>
       </c>
       <c r="E20" t="n">
-        <v>0.942383</v>
+        <v>0.9375</v>
       </c>
       <c r="F20" t="n">
-        <v>1.422852</v>
+        <v>0.96875</v>
       </c>
       <c r="G20" t="n">
-        <v>1.911133</v>
+        <v>1.21875</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>N15A</t>
+          <t>N4A</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02679</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.053819</v>
+        <v>0.125</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08094700000000001</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.108056</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KGeoMIP</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N20A</t>
+          <t>N2A</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.499296</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.998684</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>1.498507</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.997874</v>
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N3A</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.46875</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.71875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KQNodes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N2A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N3A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.46875</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.71875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N2A</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N3A</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N3B</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.21875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N4A</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A14:A16"/>
+  <mergeCells count="8">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
